--- a/data/file_generation/input/data_383/pj60 周岁以上不含村字人员名单.xlsx
+++ b/data/file_generation/input/data_383/pj60 周岁以上不含村字人员名单.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_7CDBCF0D4D54D06CDCA0B944B962C1C69AB427A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -58,295 +64,295 @@
     <t>user_89</t>
   </si>
   <si>
+    <t>******196406112554</t>
+  </si>
+  <si>
+    <t>三级残疾人</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>智力残疾</t>
+  </si>
+  <si>
+    <t>2020年残疾人生活补贴</t>
+  </si>
+  <si>
+    <t>男</t>
+  </si>
+  <si>
+    <t>汉族</t>
+  </si>
+  <si>
+    <t>非当月新增或续发</t>
+  </si>
+  <si>
+    <t>非标准变更</t>
+  </si>
+  <si>
     <t>user_90</t>
   </si>
   <si>
+    <t>******196212230026</t>
+  </si>
+  <si>
+    <t>四级残疾人</t>
+  </si>
+  <si>
+    <t>肢体残疾</t>
+  </si>
+  <si>
+    <t>女</t>
+  </si>
+  <si>
     <t>user_91</t>
   </si>
   <si>
+    <t>******195512060618</t>
+  </si>
+  <si>
+    <t>听力残疾</t>
+  </si>
+  <si>
     <t>user_92</t>
   </si>
   <si>
+    <t>******196203017215</t>
+  </si>
+  <si>
+    <t>二级残疾人</t>
+  </si>
+  <si>
+    <t>精神残疾</t>
+  </si>
+  <si>
     <t>user_93</t>
   </si>
   <si>
+    <t>******195702266692</t>
+  </si>
+  <si>
     <t>user_94</t>
   </si>
   <si>
+    <t>******194702047815</t>
+  </si>
+  <si>
     <t>user_95</t>
   </si>
   <si>
+    <t>******194701053439</t>
+  </si>
+  <si>
+    <t>一级残疾人</t>
+  </si>
+  <si>
     <t>user_96</t>
   </si>
   <si>
+    <t>******196502050736</t>
+  </si>
+  <si>
+    <t>当月续发</t>
+  </si>
+  <si>
     <t>user_97</t>
   </si>
   <si>
+    <t>******193109215174</t>
+  </si>
+  <si>
     <t>user_98</t>
   </si>
   <si>
+    <t>******19560404077X</t>
+  </si>
+  <si>
     <t>user_99</t>
   </si>
   <si>
+    <t>******195610010075</t>
+  </si>
+  <si>
     <t>user_100</t>
   </si>
   <si>
+    <t>******196504043740</t>
+  </si>
+  <si>
     <t>user_101</t>
   </si>
   <si>
+    <t>******196201060797</t>
+  </si>
+  <si>
     <t>user_102</t>
   </si>
   <si>
+    <t>******196310120904</t>
+  </si>
+  <si>
     <t>user_103</t>
   </si>
   <si>
+    <t>******194910223721</t>
+  </si>
+  <si>
     <t>user_104</t>
   </si>
   <si>
+    <t>******196304135747</t>
+  </si>
+  <si>
     <t>user_105</t>
   </si>
   <si>
+    <t>******195203133430</t>
+  </si>
+  <si>
     <t>user_106</t>
   </si>
   <si>
+    <t>******195109100739</t>
+  </si>
+  <si>
+    <t>言语残疾</t>
+  </si>
+  <si>
     <t>user_107</t>
   </si>
   <si>
+    <t>******195610280737</t>
+  </si>
+  <si>
     <t>user_108</t>
   </si>
   <si>
+    <t>******195310122737</t>
+  </si>
+  <si>
     <t>user_109</t>
   </si>
   <si>
+    <t>******195412137251</t>
+  </si>
+  <si>
     <t>user_110</t>
   </si>
   <si>
+    <t>******196205252550</t>
+  </si>
+  <si>
     <t>user_111</t>
   </si>
   <si>
+    <t>******19561125002X</t>
+  </si>
+  <si>
     <t>user_112</t>
   </si>
   <si>
+    <t>******194104142556</t>
+  </si>
+  <si>
     <t>user_113</t>
   </si>
   <si>
+    <t>******196410290521</t>
+  </si>
+  <si>
     <t>user_114</t>
   </si>
   <si>
+    <t>******196405040616</t>
+  </si>
+  <si>
     <t>user_115</t>
   </si>
   <si>
+    <t>******195710100529</t>
+  </si>
+  <si>
+    <t>视力残疾</t>
+  </si>
+  <si>
     <t>user_116</t>
   </si>
   <si>
+    <t>******196510113231</t>
+  </si>
+  <si>
     <t>user_117</t>
   </si>
   <si>
+    <t>******195707233443</t>
+  </si>
+  <si>
     <t>user_118</t>
   </si>
   <si>
+    <t>******196302153730</t>
+  </si>
+  <si>
     <t>user_119</t>
   </si>
   <si>
+    <t>******196511040054</t>
+  </si>
+  <si>
     <t>user_120</t>
   </si>
   <si>
+    <t>******195009053728</t>
+  </si>
+  <si>
     <t>user_121</t>
   </si>
   <si>
+    <t>******196112043434</t>
+  </si>
+  <si>
     <t>user_122</t>
   </si>
   <si>
+    <t>******196404030504</t>
+  </si>
+  <si>
     <t>user_123</t>
   </si>
   <si>
+    <t>******195805020038</t>
+  </si>
+  <si>
     <t>user_124</t>
   </si>
   <si>
+    <t>******195202190070</t>
+  </si>
+  <si>
     <t>user_125</t>
   </si>
   <si>
+    <t>******195206237171</t>
+  </si>
+  <si>
     <t>user_126</t>
   </si>
   <si>
+    <t>******196301300954</t>
+  </si>
+  <si>
     <t>user_127</t>
   </si>
   <si>
-    <t>******196406112554</t>
-  </si>
-  <si>
-    <t>******196212230026</t>
-  </si>
-  <si>
-    <t>******195512060618</t>
-  </si>
-  <si>
-    <t>******196203017215</t>
-  </si>
-  <si>
-    <t>******195702266692</t>
-  </si>
-  <si>
-    <t>******194702047815</t>
-  </si>
-  <si>
-    <t>******194701053439</t>
-  </si>
-  <si>
-    <t>******196502050736</t>
-  </si>
-  <si>
-    <t>******193109215174</t>
-  </si>
-  <si>
-    <t>******19560404077X</t>
-  </si>
-  <si>
-    <t>******195610010075</t>
-  </si>
-  <si>
-    <t>******196504043740</t>
-  </si>
-  <si>
-    <t>******196201060797</t>
-  </si>
-  <si>
-    <t>******196310120904</t>
-  </si>
-  <si>
-    <t>******194910223721</t>
-  </si>
-  <si>
-    <t>******196304135747</t>
-  </si>
-  <si>
-    <t>******195203133430</t>
-  </si>
-  <si>
-    <t>******195109100739</t>
-  </si>
-  <si>
-    <t>******195610280737</t>
-  </si>
-  <si>
-    <t>******195310122737</t>
-  </si>
-  <si>
-    <t>******195412137251</t>
-  </si>
-  <si>
-    <t>******196205252550</t>
-  </si>
-  <si>
-    <t>******19561125002X</t>
-  </si>
-  <si>
-    <t>******194104142556</t>
-  </si>
-  <si>
-    <t>******196410290521</t>
-  </si>
-  <si>
-    <t>******196405040616</t>
-  </si>
-  <si>
-    <t>******195710100529</t>
-  </si>
-  <si>
-    <t>******196510113231</t>
-  </si>
-  <si>
-    <t>******195707233443</t>
-  </si>
-  <si>
-    <t>******196302153730</t>
-  </si>
-  <si>
-    <t>******196511040054</t>
-  </si>
-  <si>
-    <t>******195009053728</t>
-  </si>
-  <si>
-    <t>******196112043434</t>
-  </si>
-  <si>
-    <t>******196404030504</t>
-  </si>
-  <si>
-    <t>******195805020038</t>
-  </si>
-  <si>
-    <t>******195202190070</t>
-  </si>
-  <si>
-    <t>******195206237171</t>
-  </si>
-  <si>
-    <t>******196301300954</t>
-  </si>
-  <si>
     <t>******195510102853</t>
-  </si>
-  <si>
-    <t>三级残疾人</t>
-  </si>
-  <si>
-    <t>四级残疾人</t>
-  </si>
-  <si>
-    <t>二级残疾人</t>
-  </si>
-  <si>
-    <t>一级残疾人</t>
-  </si>
-  <si>
-    <t>2025-10</t>
-  </si>
-  <si>
-    <t>智力残疾</t>
-  </si>
-  <si>
-    <t>肢体残疾</t>
-  </si>
-  <si>
-    <t>听力残疾</t>
-  </si>
-  <si>
-    <t>精神残疾</t>
-  </si>
-  <si>
-    <t>言语残疾</t>
-  </si>
-  <si>
-    <t>视力残疾</t>
-  </si>
-  <si>
-    <t>2020年残疾人生活补贴</t>
-  </si>
-  <si>
-    <t>男</t>
-  </si>
-  <si>
-    <t>女</t>
-  </si>
-  <si>
-    <t>汉族</t>
-  </si>
-  <si>
-    <t>非当月新增或续发</t>
-  </si>
-  <si>
-    <t>当月续发</t>
-  </si>
-  <si>
-    <t>非标准变更</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -406,17 +412,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -454,7 +468,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -488,6 +502,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -522,9 +537,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -697,7 +713,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -750,37 +766,37 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M2" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -788,40 +804,40 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G3">
         <v>100</v>
       </c>
       <c r="H3" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -829,40 +845,40 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L4" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M4" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -870,40 +886,40 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D5">
         <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L5" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -911,40 +927,40 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L6" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M6" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -952,40 +968,40 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G7">
         <v>100</v>
       </c>
       <c r="H7" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K7" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L7" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -993,40 +1009,40 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D8">
         <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G8">
         <v>100</v>
       </c>
       <c r="H8" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="I8" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K8" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M8" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1034,40 +1050,40 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D9">
         <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G9">
         <v>100</v>
       </c>
       <c r="H9" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I9" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K9" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L9" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="M9" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1075,40 +1091,40 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D10">
         <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G10">
         <v>100</v>
       </c>
       <c r="H10" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I10" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K10" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L10" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M10" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1116,40 +1132,40 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D11">
         <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G11">
         <v>100</v>
       </c>
       <c r="H11" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I11" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K11" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L11" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M11" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1157,40 +1173,40 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D12">
         <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G12">
         <v>100</v>
       </c>
       <c r="H12" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I12" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K12" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L12" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M12" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1198,40 +1214,40 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D13">
         <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G13">
         <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I13" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="K13" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L13" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M13" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1239,40 +1255,40 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D14">
         <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G14">
         <v>100</v>
       </c>
       <c r="H14" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="I14" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K14" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L14" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M14" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1280,40 +1296,40 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D15">
         <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G15">
         <v>100</v>
       </c>
       <c r="H15" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I15" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="K15" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L15" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M15" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1321,40 +1337,40 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D16">
         <v>76</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G16">
         <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I16" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="K16" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L16" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M16" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1362,40 +1378,40 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D17">
         <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G17">
         <v>100</v>
       </c>
       <c r="H17" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I17" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="K17" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L17" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M17" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1403,40 +1419,40 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D18">
         <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G18">
         <v>100</v>
       </c>
       <c r="H18" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I18" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K18" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L18" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M18" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1444,40 +1460,40 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D19">
         <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G19">
         <v>100</v>
       </c>
       <c r="H19" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I19" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K19" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L19" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M19" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1485,40 +1501,40 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D20">
         <v>69</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G20">
         <v>100</v>
       </c>
       <c r="H20" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I20" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K20" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L20" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M20" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1526,40 +1542,40 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D21">
         <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G21">
         <v>100</v>
       </c>
       <c r="H21" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="I21" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J21" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L21" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M21" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1567,40 +1583,40 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D22">
         <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G22">
         <v>100</v>
       </c>
       <c r="H22" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I22" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K22" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L22" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M22" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1608,7 +1624,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
         <v>73</v>
@@ -1617,31 +1633,31 @@
         <v>63</v>
       </c>
       <c r="E23" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G23">
         <v>100</v>
       </c>
       <c r="H23" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I23" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J23" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K23" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L23" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M23" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1649,40 +1665,40 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24">
         <v>69</v>
       </c>
       <c r="E24" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G24">
         <v>100</v>
       </c>
       <c r="H24" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J24" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="K24" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L24" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M24" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1690,40 +1706,40 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D25">
         <v>84</v>
       </c>
       <c r="E25" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G25">
         <v>100</v>
       </c>
       <c r="H25" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="I25" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J25" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K25" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L25" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M25" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1731,40 +1747,40 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D26">
         <v>61</v>
       </c>
       <c r="E26" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G26">
         <v>100</v>
       </c>
       <c r="H26" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I26" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J26" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="K26" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L26" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M26" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1772,40 +1788,40 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D27">
         <v>61</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G27">
         <v>100</v>
       </c>
       <c r="H27" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="I27" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J27" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K27" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L27" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M27" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1813,40 +1829,40 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D28">
         <v>68</v>
       </c>
       <c r="E28" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="F28" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G28">
         <v>100</v>
       </c>
       <c r="H28" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J28" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="K28" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L28" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M28" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1854,40 +1870,40 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D29">
         <v>60</v>
       </c>
       <c r="E29" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G29">
         <v>100</v>
       </c>
       <c r="H29" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I29" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J29" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K29" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L29" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M29" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1895,40 +1911,40 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D30">
         <v>68</v>
       </c>
       <c r="E30" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G30">
         <v>100</v>
       </c>
       <c r="H30" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J30" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="K30" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L30" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M30" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1936,40 +1952,40 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D31">
         <v>62</v>
       </c>
       <c r="E31" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G31">
         <v>100</v>
       </c>
       <c r="H31" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I31" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J31" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K31" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L31" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M31" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1977,40 +1993,40 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D32">
         <v>60</v>
       </c>
       <c r="E32" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G32">
         <v>100</v>
       </c>
       <c r="H32" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I32" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J32" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K32" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L32" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M32" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -2018,40 +2034,40 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D33">
         <v>75</v>
       </c>
       <c r="E33" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F33" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G33">
         <v>100</v>
       </c>
       <c r="H33" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I33" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J33" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="K33" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L33" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M33" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -2059,40 +2075,40 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D34">
         <v>64</v>
       </c>
       <c r="E34" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="F34" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G34">
         <v>100</v>
       </c>
       <c r="H34" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="I34" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J34" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K34" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L34" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M34" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -2100,40 +2116,40 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D35">
         <v>61</v>
       </c>
       <c r="E35" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G35">
         <v>100</v>
       </c>
       <c r="H35" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I35" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J35" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="K35" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L35" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M35" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -2141,40 +2157,40 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G36">
         <v>100</v>
       </c>
       <c r="H36" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="I36" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J36" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K36" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L36" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M36" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -2182,40 +2198,40 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D37">
         <v>73</v>
       </c>
       <c r="E37" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F37" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G37">
         <v>100</v>
       </c>
       <c r="H37" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="I37" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J37" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K37" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L37" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M37" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -2223,40 +2239,40 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D38">
         <v>73</v>
       </c>
       <c r="E38" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F38" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G38">
         <v>100</v>
       </c>
       <c r="H38" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I38" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J38" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K38" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L38" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M38" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -2264,40 +2280,40 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D39">
         <v>62</v>
       </c>
       <c r="E39" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="F39" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G39">
         <v>100</v>
       </c>
       <c r="H39" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I39" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J39" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K39" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L39" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M39" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -2305,40 +2321,40 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="D40">
         <v>70</v>
       </c>
       <c r="E40" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G40">
         <v>100</v>
       </c>
       <c r="H40" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I40" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J40" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K40" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="L40" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M40" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2347,6 +2363,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -2494,15 +2519,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2510,11 +2526,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E4BDA36-5B66-4D81-A34A-BEBF13823E1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{599EB601-A23A-469D-B664-4EE33842C3B1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{599EB601-A23A-469D-B664-4EE33842C3B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E4BDA36-5B66-4D81-A34A-BEBF13823E1F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/file_generation/input/data_383/pj60 周岁以上不含村字人员名单.xlsx
+++ b/data/file_generation/input/data_383/pj60 周岁以上不含村字人员名单.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_7CDBCF0D4D54D06CDCA0B944B962C1C69AB427A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="106">
   <si>
     <t>序号</t>
   </si>
@@ -49,9 +43,6 @@
     <t>补贴对象类型</t>
   </si>
   <si>
-    <t>性别</t>
-  </si>
-  <si>
     <t>民族</t>
   </si>
   <si>
@@ -61,298 +52,292 @@
     <t>是否当月标准变更</t>
   </si>
   <si>
-    <t>user_89</t>
-  </si>
-  <si>
-    <t>******196406112554</t>
+    <t>usr-036</t>
+  </si>
+  <si>
+    <t>usr-026</t>
+  </si>
+  <si>
+    <t>usr-028</t>
+  </si>
+  <si>
+    <t>usr-088</t>
+  </si>
+  <si>
+    <t>usr-038</t>
+  </si>
+  <si>
+    <t>usr-015</t>
+  </si>
+  <si>
+    <t>usr-053</t>
+  </si>
+  <si>
+    <t>usr-011</t>
+  </si>
+  <si>
+    <t>usr-063</t>
+  </si>
+  <si>
+    <t>usr-041</t>
+  </si>
+  <si>
+    <t>usr-066</t>
+  </si>
+  <si>
+    <t>usr-065</t>
+  </si>
+  <si>
+    <t>usr-055</t>
+  </si>
+  <si>
+    <t>usr-089</t>
+  </si>
+  <si>
+    <t>usr-016</t>
+  </si>
+  <si>
+    <t>usr-097</t>
+  </si>
+  <si>
+    <t>usr-081</t>
+  </si>
+  <si>
+    <t>usr-106</t>
+  </si>
+  <si>
+    <t>usr-093</t>
+  </si>
+  <si>
+    <t>usr-101</t>
+  </si>
+  <si>
+    <t>usr-050</t>
+  </si>
+  <si>
+    <t>usr-010</t>
+  </si>
+  <si>
+    <t>usr-092</t>
+  </si>
+  <si>
+    <t>usr-122</t>
+  </si>
+  <si>
+    <t>usr-112</t>
+  </si>
+  <si>
+    <t>usr-017</t>
+  </si>
+  <si>
+    <t>usr-018</t>
+  </si>
+  <si>
+    <t>usr-104</t>
+  </si>
+  <si>
+    <t>usr-052</t>
+  </si>
+  <si>
+    <t>usr-008</t>
+  </si>
+  <si>
+    <t>usr-073</t>
+  </si>
+  <si>
+    <t>usr-094</t>
+  </si>
+  <si>
+    <t>usr-034</t>
+  </si>
+  <si>
+    <t>usr-045</t>
+  </si>
+  <si>
+    <t>usr-103</t>
+  </si>
+  <si>
+    <t>usr-082</t>
+  </si>
+  <si>
+    <t>usr-125</t>
+  </si>
+  <si>
+    <t>usr-057</t>
+  </si>
+  <si>
+    <t>usr-108</t>
+  </si>
+  <si>
+    <t>ID-001</t>
+  </si>
+  <si>
+    <t>ID-002</t>
+  </si>
+  <si>
+    <t>ID-003</t>
+  </si>
+  <si>
+    <t>ID-004</t>
+  </si>
+  <si>
+    <t>ID-005</t>
+  </si>
+  <si>
+    <t>ID-006</t>
+  </si>
+  <si>
+    <t>ID-007</t>
+  </si>
+  <si>
+    <t>ID-008</t>
+  </si>
+  <si>
+    <t>ID-009</t>
+  </si>
+  <si>
+    <t>ID-010</t>
+  </si>
+  <si>
+    <t>ID-011</t>
+  </si>
+  <si>
+    <t>ID-012</t>
+  </si>
+  <si>
+    <t>ID-013</t>
+  </si>
+  <si>
+    <t>ID-014</t>
+  </si>
+  <si>
+    <t>ID-015</t>
+  </si>
+  <si>
+    <t>ID-016</t>
+  </si>
+  <si>
+    <t>ID-017</t>
+  </si>
+  <si>
+    <t>ID-018</t>
+  </si>
+  <si>
+    <t>ID-019</t>
+  </si>
+  <si>
+    <t>ID-020</t>
+  </si>
+  <si>
+    <t>ID-021</t>
+  </si>
+  <si>
+    <t>ID-022</t>
+  </si>
+  <si>
+    <t>ID-023</t>
+  </si>
+  <si>
+    <t>ID-024</t>
+  </si>
+  <si>
+    <t>ID-025</t>
+  </si>
+  <si>
+    <t>ID-026</t>
+  </si>
+  <si>
+    <t>ID-027</t>
+  </si>
+  <si>
+    <t>ID-028</t>
+  </si>
+  <si>
+    <t>ID-029</t>
+  </si>
+  <si>
+    <t>ID-030</t>
+  </si>
+  <si>
+    <t>ID-031</t>
+  </si>
+  <si>
+    <t>ID-032</t>
+  </si>
+  <si>
+    <t>ID-033</t>
+  </si>
+  <si>
+    <t>ID-034</t>
+  </si>
+  <si>
+    <t>ID-035</t>
+  </si>
+  <si>
+    <t>ID-036</t>
+  </si>
+  <si>
+    <t>ID-037</t>
+  </si>
+  <si>
+    <t>ID-038</t>
+  </si>
+  <si>
+    <t>ID-039</t>
   </si>
   <si>
     <t>三级残疾人</t>
   </si>
   <si>
+    <t>四级残疾人</t>
+  </si>
+  <si>
+    <t>二级残疾人</t>
+  </si>
+  <si>
+    <t>一级残疾人</t>
+  </si>
+  <si>
     <t>2025-10</t>
   </si>
   <si>
     <t>智力残疾</t>
   </si>
   <si>
+    <t>肢体残疾</t>
+  </si>
+  <si>
+    <t>听力残疾</t>
+  </si>
+  <si>
+    <t>精神残疾</t>
+  </si>
+  <si>
+    <t>言语残疾</t>
+  </si>
+  <si>
+    <t>视力残疾</t>
+  </si>
+  <si>
     <t>2020年残疾人生活补贴</t>
   </si>
   <si>
-    <t>男</t>
-  </si>
-  <si>
     <t>汉族</t>
   </si>
   <si>
     <t>非当月新增或续发</t>
   </si>
   <si>
+    <t>当月续发</t>
+  </si>
+  <si>
     <t>非标准变更</t>
-  </si>
-  <si>
-    <t>user_90</t>
-  </si>
-  <si>
-    <t>******196212230026</t>
-  </si>
-  <si>
-    <t>四级残疾人</t>
-  </si>
-  <si>
-    <t>肢体残疾</t>
-  </si>
-  <si>
-    <t>女</t>
-  </si>
-  <si>
-    <t>user_91</t>
-  </si>
-  <si>
-    <t>******195512060618</t>
-  </si>
-  <si>
-    <t>听力残疾</t>
-  </si>
-  <si>
-    <t>user_92</t>
-  </si>
-  <si>
-    <t>******196203017215</t>
-  </si>
-  <si>
-    <t>二级残疾人</t>
-  </si>
-  <si>
-    <t>精神残疾</t>
-  </si>
-  <si>
-    <t>user_93</t>
-  </si>
-  <si>
-    <t>******195702266692</t>
-  </si>
-  <si>
-    <t>user_94</t>
-  </si>
-  <si>
-    <t>******194702047815</t>
-  </si>
-  <si>
-    <t>user_95</t>
-  </si>
-  <si>
-    <t>******194701053439</t>
-  </si>
-  <si>
-    <t>一级残疾人</t>
-  </si>
-  <si>
-    <t>user_96</t>
-  </si>
-  <si>
-    <t>******196502050736</t>
-  </si>
-  <si>
-    <t>当月续发</t>
-  </si>
-  <si>
-    <t>user_97</t>
-  </si>
-  <si>
-    <t>******193109215174</t>
-  </si>
-  <si>
-    <t>user_98</t>
-  </si>
-  <si>
-    <t>******19560404077X</t>
-  </si>
-  <si>
-    <t>user_99</t>
-  </si>
-  <si>
-    <t>******195610010075</t>
-  </si>
-  <si>
-    <t>user_100</t>
-  </si>
-  <si>
-    <t>******196504043740</t>
-  </si>
-  <si>
-    <t>user_101</t>
-  </si>
-  <si>
-    <t>******196201060797</t>
-  </si>
-  <si>
-    <t>user_102</t>
-  </si>
-  <si>
-    <t>******196310120904</t>
-  </si>
-  <si>
-    <t>user_103</t>
-  </si>
-  <si>
-    <t>******194910223721</t>
-  </si>
-  <si>
-    <t>user_104</t>
-  </si>
-  <si>
-    <t>******196304135747</t>
-  </si>
-  <si>
-    <t>user_105</t>
-  </si>
-  <si>
-    <t>******195203133430</t>
-  </si>
-  <si>
-    <t>user_106</t>
-  </si>
-  <si>
-    <t>******195109100739</t>
-  </si>
-  <si>
-    <t>言语残疾</t>
-  </si>
-  <si>
-    <t>user_107</t>
-  </si>
-  <si>
-    <t>******195610280737</t>
-  </si>
-  <si>
-    <t>user_108</t>
-  </si>
-  <si>
-    <t>******195310122737</t>
-  </si>
-  <si>
-    <t>user_109</t>
-  </si>
-  <si>
-    <t>******195412137251</t>
-  </si>
-  <si>
-    <t>user_110</t>
-  </si>
-  <si>
-    <t>******196205252550</t>
-  </si>
-  <si>
-    <t>user_111</t>
-  </si>
-  <si>
-    <t>******19561125002X</t>
-  </si>
-  <si>
-    <t>user_112</t>
-  </si>
-  <si>
-    <t>******194104142556</t>
-  </si>
-  <si>
-    <t>user_113</t>
-  </si>
-  <si>
-    <t>******196410290521</t>
-  </si>
-  <si>
-    <t>user_114</t>
-  </si>
-  <si>
-    <t>******196405040616</t>
-  </si>
-  <si>
-    <t>user_115</t>
-  </si>
-  <si>
-    <t>******195710100529</t>
-  </si>
-  <si>
-    <t>视力残疾</t>
-  </si>
-  <si>
-    <t>user_116</t>
-  </si>
-  <si>
-    <t>******196510113231</t>
-  </si>
-  <si>
-    <t>user_117</t>
-  </si>
-  <si>
-    <t>******195707233443</t>
-  </si>
-  <si>
-    <t>user_118</t>
-  </si>
-  <si>
-    <t>******196302153730</t>
-  </si>
-  <si>
-    <t>user_119</t>
-  </si>
-  <si>
-    <t>******196511040054</t>
-  </si>
-  <si>
-    <t>user_120</t>
-  </si>
-  <si>
-    <t>******195009053728</t>
-  </si>
-  <si>
-    <t>user_121</t>
-  </si>
-  <si>
-    <t>******196112043434</t>
-  </si>
-  <si>
-    <t>user_122</t>
-  </si>
-  <si>
-    <t>******196404030504</t>
-  </si>
-  <si>
-    <t>user_123</t>
-  </si>
-  <si>
-    <t>******195805020038</t>
-  </si>
-  <si>
-    <t>user_124</t>
-  </si>
-  <si>
-    <t>******195202190070</t>
-  </si>
-  <si>
-    <t>user_125</t>
-  </si>
-  <si>
-    <t>******195206237171</t>
-  </si>
-  <si>
-    <t>user_126</t>
-  </si>
-  <si>
-    <t>******196301300954</t>
-  </si>
-  <si>
-    <t>user_127</t>
-  </si>
-  <si>
-    <t>******195510102853</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -412,25 +397,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -468,7 +445,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -502,7 +479,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -537,10 +513,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -713,11 +688,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,836 +729,773 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="D2">
         <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D3">
         <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G3">
         <v>100</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D4">
         <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D5">
         <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D6">
         <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G6">
         <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K6" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D7">
         <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G7">
         <v>100</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K7" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D8">
         <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G8">
         <v>100</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J8" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="D9">
         <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G9">
         <v>100</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J9" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K9" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="L9" t="s">
-        <v>44</v>
-      </c>
-      <c r="M9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D10">
         <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G10">
         <v>100</v>
       </c>
       <c r="H10" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J10" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K10" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D11">
         <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G11">
         <v>100</v>
       </c>
       <c r="H11" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J11" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K11" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D12">
         <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G12">
         <v>100</v>
       </c>
       <c r="H12" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J12" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K12" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L12" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D13">
         <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G13">
         <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J13" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="K13" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D14">
         <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G14">
         <v>100</v>
       </c>
       <c r="H14" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K14" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D15">
         <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G15">
         <v>100</v>
       </c>
       <c r="H15" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J15" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="K15" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D16">
         <v>76</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G16">
         <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J16" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="K16" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D17">
         <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G17">
         <v>100</v>
       </c>
       <c r="H17" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J17" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="K17" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D18">
         <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G18">
         <v>100</v>
       </c>
       <c r="H18" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J18" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K18" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D19">
         <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G19">
         <v>100</v>
       </c>
       <c r="H19" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="I19" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K19" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L19" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D20">
         <v>69</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G20">
         <v>100</v>
       </c>
       <c r="H20" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I20" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K20" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D21">
         <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G21">
         <v>100</v>
       </c>
       <c r="H21" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K21" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
         <v>71</v>
@@ -1592,769 +1504,712 @@
         <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G22">
         <v>100</v>
       </c>
       <c r="H22" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K22" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
         <v>72</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
       </c>
       <c r="D23">
         <v>63</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G23">
         <v>100</v>
       </c>
       <c r="H23" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I23" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K23" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L23" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D24">
         <v>69</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G24">
         <v>100</v>
       </c>
       <c r="H24" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J24" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="K24" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D25">
         <v>84</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G25">
         <v>100</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="I25" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J25" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K25" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L25" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D26">
         <v>61</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G26">
         <v>100</v>
       </c>
       <c r="H26" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I26" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J26" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="K26" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L26" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D27">
         <v>61</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G27">
         <v>100</v>
       </c>
       <c r="H27" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="I27" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J27" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K27" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D28">
         <v>68</v>
       </c>
       <c r="E28" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G28">
         <v>100</v>
       </c>
       <c r="H28" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J28" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="K28" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D29">
         <v>60</v>
       </c>
       <c r="E29" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G29">
         <v>100</v>
       </c>
       <c r="H29" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I29" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J29" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K29" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L29" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D30">
         <v>68</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G30">
         <v>100</v>
       </c>
       <c r="H30" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="I30" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J30" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="K30" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L30" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D31">
         <v>62</v>
       </c>
       <c r="E31" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G31">
         <v>100</v>
       </c>
       <c r="H31" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I31" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J31" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K31" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D32">
         <v>60</v>
       </c>
       <c r="E32" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F32" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G32">
         <v>100</v>
       </c>
       <c r="H32" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I32" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J32" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K32" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L32" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D33">
         <v>75</v>
       </c>
       <c r="E33" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G33">
         <v>100</v>
       </c>
       <c r="H33" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I33" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J33" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="K33" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L33" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D34">
         <v>64</v>
       </c>
       <c r="E34" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G34">
         <v>100</v>
       </c>
       <c r="H34" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J34" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K34" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L34" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D35">
         <v>61</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G35">
         <v>100</v>
       </c>
       <c r="H35" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="I35" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J35" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="K35" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L35" t="s">
-        <v>21</v>
-      </c>
-      <c r="M35" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D36">
         <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G36">
         <v>100</v>
       </c>
       <c r="H36" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="I36" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J36" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K36" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L36" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D37">
         <v>73</v>
       </c>
       <c r="E37" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G37">
         <v>100</v>
       </c>
       <c r="H37" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="I37" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J37" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K37" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L37" t="s">
-        <v>21</v>
-      </c>
-      <c r="M37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="D38">
         <v>73</v>
       </c>
       <c r="E38" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G38">
         <v>100</v>
       </c>
       <c r="H38" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I38" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J38" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K38" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L38" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D39">
         <v>62</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G39">
         <v>100</v>
       </c>
       <c r="H39" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I39" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K39" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L39" t="s">
-        <v>21</v>
-      </c>
-      <c r="M39" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D40">
         <v>70</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G40">
         <v>100</v>
       </c>
       <c r="H40" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I40" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="K40" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L40" t="s">
-        <v>21</v>
-      </c>
-      <c r="M40" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2363,15 +2218,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -2519,6 +2365,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2526,13 +2381,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{599EB601-A23A-469D-B664-4EE33842C3B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B142BF1B-FC6C-46C9-B042-3E757B1E83CC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E4BDA36-5B66-4D81-A34A-BEBF13823E1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7192B8CC-A5BC-4424-9753-94EA560CEFEE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C32FCB14-13BE-48C7-BE5B-BAFB72190E5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{765DE14E-906E-4EF8-9A0B-F508D191385D}"/>
 </file>